--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126590448</v>
+        <v>126590430</v>
       </c>
       <c r="B2" t="n">
-        <v>91541</v>
+        <v>91319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725334</v>
+        <v>725325</v>
       </c>
       <c r="R2" t="n">
-        <v>7179671</v>
+        <v>7179643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126590430</v>
+        <v>126590448</v>
       </c>
       <c r="B3" t="n">
-        <v>91245</v>
+        <v>91615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725325</v>
+        <v>725334</v>
       </c>
       <c r="R3" t="n">
-        <v>7179643</v>
+        <v>7179671</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126590432</v>
+        <v>126590446</v>
       </c>
       <c r="B5" t="n">
-        <v>91245</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,34 +985,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725345</v>
+        <v>725318</v>
       </c>
       <c r="R5" t="n">
-        <v>7179625</v>
+        <v>7179668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,6 +1053,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126590446</v>
+        <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>91319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,42 +1095,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725318</v>
+        <v>725345</v>
       </c>
       <c r="R6" t="n">
-        <v>7179668</v>
+        <v>7179625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,11 +1155,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,7 +1294,7 @@
         <v>126590427</v>
       </c>
       <c r="B8" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126590436</v>
+        <v>126590452</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1509,42 +1509,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725097</v>
+        <v>725223</v>
       </c>
       <c r="R10" t="n">
-        <v>7179606</v>
+        <v>7179775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,11 +1569,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126590452</v>
+        <v>126590436</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,34 +1606,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725223</v>
+        <v>725097</v>
       </c>
       <c r="R11" t="n">
-        <v>7179775</v>
+        <v>7179606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,6 +1674,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126590449</v>
+        <v>126590437</v>
       </c>
       <c r="B12" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,34 +1716,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725329</v>
+        <v>725139</v>
       </c>
       <c r="R12" t="n">
-        <v>7179687</v>
+        <v>7179711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1784,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126590437</v>
+        <v>126590449</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>80114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,42 +1826,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725139</v>
+        <v>725329</v>
       </c>
       <c r="R13" t="n">
-        <v>7179711</v>
+        <v>7179687</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1881,11 +1886,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1915,7 +1915,7 @@
         <v>126590453</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126590435</v>
+        <v>126590454</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2020,42 +2020,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725121</v>
+        <v>725304</v>
       </c>
       <c r="R15" t="n">
-        <v>7179544</v>
+        <v>7179667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,11 +2080,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,10 +2106,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126590454</v>
+        <v>126590435</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,34 +2117,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725304</v>
+        <v>725121</v>
       </c>
       <c r="R16" t="n">
-        <v>7179667</v>
+        <v>7179544</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,6 +2185,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2216,10 +2216,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126590429</v>
+        <v>126590440</v>
       </c>
       <c r="B17" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,34 +2227,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725334</v>
+        <v>725273</v>
       </c>
       <c r="R17" t="n">
-        <v>7179675</v>
+        <v>7179689</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2287,6 +2295,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2313,10 +2326,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126590440</v>
+        <v>126590429</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>91319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,42 +2337,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725273</v>
+        <v>725334</v>
       </c>
       <c r="R18" t="n">
-        <v>7179689</v>
+        <v>7179675</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2392,11 +2397,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2423,45 +2423,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126590428</v>
+        <v>126590443</v>
       </c>
       <c r="B19" t="n">
-        <v>91603</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725348</v>
+        <v>725244</v>
       </c>
       <c r="R19" t="n">
-        <v>7179632</v>
+        <v>7179447</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2494,6 +2502,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2520,53 +2533,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126590443</v>
+        <v>126590428</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>91677</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725244</v>
+        <v>725348</v>
       </c>
       <c r="R20" t="n">
-        <v>7179447</v>
+        <v>7179632</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2599,11 +2604,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2630,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126590442</v>
+        <v>126590455</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,42 +2641,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>725329</v>
+        <v>725352</v>
       </c>
       <c r="R21" t="n">
-        <v>7179542</v>
+        <v>7179640</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2709,11 +2701,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2740,10 +2727,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126590455</v>
+        <v>126590442</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2751,34 +2738,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>725352</v>
+        <v>725329</v>
       </c>
       <c r="R22" t="n">
-        <v>7179640</v>
+        <v>7179542</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,6 +2806,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126590433</v>
+        <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>91333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2848,42 +2848,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>725166</v>
+        <v>725319</v>
       </c>
       <c r="R23" t="n">
-        <v>7179793</v>
+        <v>7179634</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2916,11 +2908,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2947,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126590450</v>
+        <v>126590433</v>
       </c>
       <c r="B24" t="n">
-        <v>91259</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,34 +2945,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>725319</v>
+        <v>725166</v>
       </c>
       <c r="R24" t="n">
-        <v>7179634</v>
+        <v>7179793</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,6 +3013,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3047,7 +3047,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590430</v>
       </c>
       <c r="B2" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126590448</v>
       </c>
       <c r="B3" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126590446</v>
+        <v>126590432</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>91325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,42 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725318</v>
+        <v>725345</v>
       </c>
       <c r="R5" t="n">
-        <v>7179668</v>
+        <v>7179625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,11 +1045,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126590432</v>
+        <v>126590446</v>
       </c>
       <c r="B6" t="n">
-        <v>91319</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,34 +1082,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725345</v>
+        <v>725318</v>
       </c>
       <c r="R6" t="n">
-        <v>7179625</v>
+        <v>7179668</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1155,6 +1150,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,7 +1294,7 @@
         <v>126590427</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126590452</v>
+        <v>126590436</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1509,34 +1509,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725223</v>
+        <v>725097</v>
       </c>
       <c r="R10" t="n">
-        <v>7179775</v>
+        <v>7179606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,6 +1577,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126590436</v>
+        <v>126590452</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1606,42 +1619,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725097</v>
+        <v>725223</v>
       </c>
       <c r="R11" t="n">
-        <v>7179606</v>
+        <v>7179775</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,11 +1679,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126590437</v>
+        <v>126590449</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,42 +1716,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725139</v>
+        <v>725329</v>
       </c>
       <c r="R12" t="n">
-        <v>7179711</v>
+        <v>7179687</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,11 +1776,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1815,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126590449</v>
+        <v>126590437</v>
       </c>
       <c r="B13" t="n">
-        <v>80114</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1826,34 +1813,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725329</v>
+        <v>725139</v>
       </c>
       <c r="R13" t="n">
-        <v>7179687</v>
+        <v>7179711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,6 +1881,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1915,7 +1915,7 @@
         <v>126590453</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>126590454</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>126590429</v>
       </c>
       <c r="B18" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,53 +2423,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126590443</v>
+        <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>91683</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725244</v>
+        <v>725348</v>
       </c>
       <c r="R19" t="n">
-        <v>7179447</v>
+        <v>7179632</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,11 +2494,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,45 +2520,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126590428</v>
+        <v>126590443</v>
       </c>
       <c r="B20" t="n">
-        <v>91677</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725348</v>
+        <v>725244</v>
       </c>
       <c r="R20" t="n">
-        <v>7179632</v>
+        <v>7179447</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,6 +2599,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,7 +2633,7 @@
         <v>126590455</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126590450</v>
+        <v>126590433</v>
       </c>
       <c r="B23" t="n">
-        <v>91333</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2848,34 +2848,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>725319</v>
+        <v>725166</v>
       </c>
       <c r="R23" t="n">
-        <v>7179634</v>
+        <v>7179793</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2908,6 +2916,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2934,10 +2947,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126590433</v>
+        <v>126590450</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>91339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,42 +2958,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>725166</v>
+        <v>725319</v>
       </c>
       <c r="R24" t="n">
-        <v>7179793</v>
+        <v>7179634</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3013,11 +3018,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3047,7 +3047,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126590430</v>
+        <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91325</v>
+        <v>91621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725325</v>
+        <v>725334</v>
       </c>
       <c r="R2" t="n">
-        <v>7179643</v>
+        <v>7179671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126590448</v>
+        <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91621</v>
+        <v>91325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725334</v>
+        <v>725325</v>
       </c>
       <c r="R3" t="n">
-        <v>7179671</v>
+        <v>7179643</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126590432</v>
+        <v>126590446</v>
       </c>
       <c r="B5" t="n">
-        <v>91325</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,34 +985,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725345</v>
+        <v>725318</v>
       </c>
       <c r="R5" t="n">
-        <v>7179625</v>
+        <v>7179668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,6 +1053,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126590446</v>
+        <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>91325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,42 +1095,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725318</v>
+        <v>725345</v>
       </c>
       <c r="R6" t="n">
-        <v>7179668</v>
+        <v>7179625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,11 +1155,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1498,10 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126590436</v>
+        <v>126590452</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1509,42 +1509,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725097</v>
+        <v>725223</v>
       </c>
       <c r="R10" t="n">
-        <v>7179606</v>
+        <v>7179775</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,11 +1569,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126590452</v>
+        <v>126590436</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,34 +1606,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725223</v>
+        <v>725097</v>
       </c>
       <c r="R11" t="n">
-        <v>7179775</v>
+        <v>7179606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,6 +1674,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2009,10 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126590454</v>
+        <v>126590435</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2020,34 +2020,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725304</v>
+        <v>725121</v>
       </c>
       <c r="R15" t="n">
-        <v>7179667</v>
+        <v>7179544</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,6 +2088,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126590435</v>
+        <v>126590454</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2117,42 +2130,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725121</v>
+        <v>725304</v>
       </c>
       <c r="R16" t="n">
-        <v>7179544</v>
+        <v>7179667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2185,11 +2190,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2216,10 +2216,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126590440</v>
+        <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,42 +2227,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725273</v>
+        <v>725334</v>
       </c>
       <c r="R17" t="n">
-        <v>7179689</v>
+        <v>7179675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2295,11 +2287,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2326,10 +2313,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126590429</v>
+        <v>126590440</v>
       </c>
       <c r="B18" t="n">
-        <v>91325</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,34 +2324,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725334</v>
+        <v>725273</v>
       </c>
       <c r="R18" t="n">
-        <v>7179675</v>
+        <v>7179689</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,6 +2392,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126590433</v>
+        <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>91339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2848,42 +2848,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>725166</v>
+        <v>725319</v>
       </c>
       <c r="R23" t="n">
-        <v>7179793</v>
+        <v>7179634</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2916,11 +2908,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2947,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126590450</v>
+        <v>126590433</v>
       </c>
       <c r="B24" t="n">
-        <v>91339</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,34 +2945,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>725319</v>
+        <v>725166</v>
       </c>
       <c r="R24" t="n">
-        <v>7179634</v>
+        <v>7179793</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,6 +3013,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91621</v>
+        <v>91800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91325</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>126590445</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,14 +978,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>126590446</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,14 +1092,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>91325</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,14 +1193,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>126590438</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,14 +1307,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>126590427</v>
       </c>
       <c r="B8" t="n">
-        <v>79046</v>
+        <v>79152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,14 +1408,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>126590441</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,14 +1522,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>126590452</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,14 +1623,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>126590436</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,14 +1737,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>126590449</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>80225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,14 +1838,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>126590437</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,14 +1952,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>126590453</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,14 +2053,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>126590435</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,14 +2167,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>126590454</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,14 +2268,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>91325</v>
+        <v>91504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,14 +2369,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>126590440</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,14 +2483,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91683</v>
+        <v>91862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,14 +2584,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>126590443</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,14 +2698,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>126590455</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,14 +2799,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>126590442</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,14 +2913,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>91339</v>
+        <v>91518</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2930,14 +3014,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>126590433</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,14 +3128,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91343</v>
+        <v>91522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3137,14 +3229,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91325</v>
+        <v>91504</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3234,7 +3330,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126590445</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126590446</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>126590438</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>126590427</v>
       </c>
       <c r="B8" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>126590441</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>126590452</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>126590436</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>126590449</v>
       </c>
       <c r="B12" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>126590437</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>126590453</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>126590435</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>126590454</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>126590440</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>126590443</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>126590455</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>126590442</v>
       </c>
       <c r="B22" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>126590433</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126590445</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126590446</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>126590438</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>126590427</v>
       </c>
       <c r="B8" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>126590441</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>126590452</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>126590436</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>126590449</v>
       </c>
       <c r="B12" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>126590437</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>126590453</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>126590435</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>126590454</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>126590440</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>126590443</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>126590455</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>126590442</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>126590433</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>126590427</v>
       </c>
       <c r="B8" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>126590452</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>126590449</v>
       </c>
       <c r="B12" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>126590453</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>126590454</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>126590455</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126590445</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126590446</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>126590438</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>126590427</v>
       </c>
       <c r="B8" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>126590441</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>126590452</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>126590436</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>126590449</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>126590437</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>126590453</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>126590435</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>126590454</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>126590440</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>126590443</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>126590455</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>126590442</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>126590433</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126590445</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126590446</v>
       </c>
       <c r="B5" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>126590438</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>126590427</v>
       </c>
       <c r="B8" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>126590441</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>126590452</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>126590436</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>126590449</v>
       </c>
       <c r="B12" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>126590437</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>126590453</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>126590435</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>126590454</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>126590440</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>126590443</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>126590455</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>126590442</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>126590433</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3156,14 +3156,10 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>126590427</v>
       </c>
       <c r="B8" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>126590452</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>126590449</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>126590453</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>126590454</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>126590455</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>126590427</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>126590452</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>126590449</v>
       </c>
       <c r="B12" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>126590453</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>126590454</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>126590455</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>126590432</v>
       </c>
       <c r="B6" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>126590450</v>
       </c>
       <c r="B23" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>126590451</v>
       </c>
       <c r="B25" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126590431</v>
       </c>
       <c r="B26" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126590448</v>
+        <v>126590430</v>
       </c>
       <c r="B2" t="n">
-        <v>91847</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725334</v>
+        <v>725325</v>
       </c>
       <c r="R2" t="n">
-        <v>7179671</v>
+        <v>7179643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126590430</v>
+        <v>126590448</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>91847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725325</v>
+        <v>725334</v>
       </c>
       <c r="R3" t="n">
-        <v>7179643</v>
+        <v>7179671</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126590449</v>
+        <v>126590437</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,34 +1756,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725329</v>
+        <v>725139</v>
       </c>
       <c r="R12" t="n">
-        <v>7179687</v>
+        <v>7179711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,6 +1824,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126590437</v>
+        <v>126590449</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,42 +1870,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725139</v>
+        <v>725329</v>
       </c>
       <c r="R13" t="n">
-        <v>7179711</v>
+        <v>7179687</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,11 +1930,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126590435</v>
+        <v>126590454</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,42 +2072,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725121</v>
+        <v>725304</v>
       </c>
       <c r="R15" t="n">
-        <v>7179544</v>
+        <v>7179667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,11 +2132,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2175,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126590454</v>
+        <v>126590435</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2186,34 +2173,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725304</v>
+        <v>725121</v>
       </c>
       <c r="R16" t="n">
-        <v>7179667</v>
+        <v>7179544</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,6 +2241,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2276,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126590429</v>
+        <v>126590440</v>
       </c>
       <c r="B17" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,34 +2287,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725334</v>
+        <v>725273</v>
       </c>
       <c r="R17" t="n">
-        <v>7179675</v>
+        <v>7179689</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2347,6 +2355,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126590440</v>
+        <v>126590429</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,42 +2401,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725273</v>
+        <v>725334</v>
       </c>
       <c r="R18" t="n">
-        <v>7179689</v>
+        <v>7179675</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,11 +2461,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2491,45 +2491,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126590428</v>
+        <v>126590443</v>
       </c>
       <c r="B19" t="n">
-        <v>91920</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725348</v>
+        <v>725244</v>
       </c>
       <c r="R19" t="n">
-        <v>7179632</v>
+        <v>7179447</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,6 +2570,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,53 +2605,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126590443</v>
+        <v>126590428</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>91920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725244</v>
+        <v>725348</v>
       </c>
       <c r="R20" t="n">
-        <v>7179447</v>
+        <v>7179632</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,11 +2676,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126590430</v>
+        <v>126590448</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>91847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725325</v>
+        <v>725334</v>
       </c>
       <c r="R2" t="n">
-        <v>7179643</v>
+        <v>7179671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126590448</v>
+        <v>126590430</v>
       </c>
       <c r="B3" t="n">
-        <v>91847</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725334</v>
+        <v>725325</v>
       </c>
       <c r="R3" t="n">
-        <v>7179671</v>
+        <v>7179643</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126590437</v>
+        <v>126590449</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,42 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725139</v>
+        <v>725329</v>
       </c>
       <c r="R12" t="n">
-        <v>7179711</v>
+        <v>7179687</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126590449</v>
+        <v>126590437</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,34 +1857,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725329</v>
+        <v>725139</v>
       </c>
       <c r="R13" t="n">
-        <v>7179687</v>
+        <v>7179711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,6 +1925,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126590454</v>
+        <v>126590435</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,34 +2072,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725304</v>
+        <v>725121</v>
       </c>
       <c r="R15" t="n">
-        <v>7179667</v>
+        <v>7179544</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,6 +2140,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126590435</v>
+        <v>126590454</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2173,42 +2186,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725121</v>
+        <v>725304</v>
       </c>
       <c r="R16" t="n">
-        <v>7179544</v>
+        <v>7179667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,11 +2246,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2276,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126590440</v>
+        <v>126590429</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,42 +2287,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725273</v>
+        <v>725334</v>
       </c>
       <c r="R17" t="n">
-        <v>7179689</v>
+        <v>7179675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,11 +2347,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126590429</v>
+        <v>126590440</v>
       </c>
       <c r="B18" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2401,34 +2388,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725334</v>
+        <v>725273</v>
       </c>
       <c r="R18" t="n">
-        <v>7179675</v>
+        <v>7179689</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2461,6 +2456,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2491,53 +2491,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126590443</v>
+        <v>126590428</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>91920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725244</v>
+        <v>725348</v>
       </c>
       <c r="R19" t="n">
-        <v>7179447</v>
+        <v>7179632</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2570,11 +2562,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,45 +2592,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126590428</v>
+        <v>126590443</v>
       </c>
       <c r="B20" t="n">
-        <v>91920</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725348</v>
+        <v>725244</v>
       </c>
       <c r="R20" t="n">
-        <v>7179632</v>
+        <v>7179447</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,6 +2671,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126590448</v>
+        <v>126590427</v>
       </c>
       <c r="B2" t="n">
-        <v>91847</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725334</v>
+        <v>725301</v>
       </c>
       <c r="R2" t="n">
-        <v>7179671</v>
+        <v>7179436</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126590430</v>
+        <v>126590448</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725325</v>
+        <v>725334</v>
       </c>
       <c r="R3" t="n">
-        <v>7179643</v>
+        <v>7179671</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126590445</v>
+        <v>126590429</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725301</v>
+        <v>725334</v>
       </c>
       <c r="R4" t="n">
-        <v>7179635</v>
+        <v>7179675</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126590446</v>
+        <v>126590430</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,42 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725318</v>
+        <v>725325</v>
       </c>
       <c r="R5" t="n">
-        <v>7179668</v>
+        <v>7179643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,11 +1049,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färsk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126590432</v>
+        <v>126590431</v>
       </c>
       <c r="B6" t="n">
-        <v>91549</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725345</v>
+        <v>725397</v>
       </c>
       <c r="R6" t="n">
-        <v>7179625</v>
+        <v>7179471</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126590438</v>
+        <v>126590432</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1212,42 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725155</v>
+        <v>725345</v>
       </c>
       <c r="R7" t="n">
-        <v>7179752</v>
+        <v>7179625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126590427</v>
+        <v>126590450</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725301</v>
+        <v>725319</v>
       </c>
       <c r="R8" t="n">
-        <v>7179436</v>
+        <v>7179634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,53 +1382,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126590441</v>
+        <v>126590428</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>92281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725354</v>
+        <v>725348</v>
       </c>
       <c r="R9" t="n">
-        <v>7179639</v>
+        <v>7179632</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1453,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,11 +1486,11 @@
         <v>126590452</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1631,53 +1584,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126590436</v>
+        <v>126590453</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725097</v>
+        <v>725173</v>
       </c>
       <c r="R11" t="n">
-        <v>7179606</v>
+        <v>7179703</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,11 +1655,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126590449</v>
+        <v>126590454</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725329</v>
+        <v>725304</v>
       </c>
       <c r="R12" t="n">
-        <v>7179687</v>
+        <v>7179667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,53 +1786,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126590437</v>
+        <v>126590455</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725139</v>
+        <v>725352</v>
       </c>
       <c r="R13" t="n">
-        <v>7179711</v>
+        <v>7179640</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,11 +1857,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126590453</v>
+        <v>126590449</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,21 +1898,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1995,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725173</v>
+        <v>725329</v>
       </c>
       <c r="R14" t="n">
-        <v>7179703</v>
+        <v>7179687</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,27 +1988,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126590435</v>
+        <v>126590445</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2094,7 +2021,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2104,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725121</v>
+        <v>725301</v>
       </c>
       <c r="R15" t="n">
-        <v>7179544</v>
+        <v>7179635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,11 +2067,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2175,45 +2097,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126590454</v>
+        <v>126590446</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725304</v>
+        <v>725318</v>
       </c>
       <c r="R16" t="n">
-        <v>7179667</v>
+        <v>7179668</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,6 +2176,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färsk</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2276,10 +2211,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126590429</v>
+        <v>126590433</v>
       </c>
       <c r="B17" t="n">
-        <v>91549</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,34 +2222,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725334</v>
+        <v>725166</v>
       </c>
       <c r="R17" t="n">
-        <v>7179675</v>
+        <v>7179793</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2347,6 +2290,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126590440</v>
+        <v>126590435</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,10 +2368,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725273</v>
+        <v>725121</v>
       </c>
       <c r="R18" t="n">
-        <v>7179689</v>
+        <v>7179544</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,45 +2439,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126590428</v>
+        <v>126590436</v>
       </c>
       <c r="B19" t="n">
-        <v>91920</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725348</v>
+        <v>725097</v>
       </c>
       <c r="R19" t="n">
-        <v>7179632</v>
+        <v>7179606</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,6 +2518,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2592,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126590443</v>
+        <v>126590437</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725244</v>
+        <v>725139</v>
       </c>
       <c r="R20" t="n">
-        <v>7179447</v>
+        <v>7179711</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,10 +2667,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126590455</v>
+        <v>126590438</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2717,34 +2678,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>725352</v>
+        <v>725155</v>
       </c>
       <c r="R21" t="n">
-        <v>7179640</v>
+        <v>7179752</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2777,6 +2746,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2807,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126590442</v>
+        <v>126590439</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2814,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2850,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>725329</v>
+        <v>725273</v>
       </c>
       <c r="R22" t="n">
-        <v>7179542</v>
+        <v>7179689</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2864,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2921,10 +2895,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126590450</v>
+        <v>126590441</v>
       </c>
       <c r="B23" t="n">
-        <v>91563</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,34 +2906,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>725319</v>
+        <v>725354</v>
       </c>
       <c r="R23" t="n">
-        <v>7179634</v>
+        <v>7179639</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,6 +2974,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3022,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126590433</v>
+        <v>126590442</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3055,7 +3042,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3065,10 +3052,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>725166</v>
+        <v>725329</v>
       </c>
       <c r="R24" t="n">
-        <v>7179793</v>
+        <v>7179542</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126590451</v>
+        <v>126590443</v>
       </c>
       <c r="B25" t="n">
-        <v>91569</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,30 +3134,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725369</v>
+        <v>725244</v>
       </c>
       <c r="R25" t="n">
-        <v>7179515</v>
+        <v>7179447</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3203,6 +3202,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,10 +3237,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126590431</v>
+        <v>126590456</v>
       </c>
       <c r="B26" t="n">
-        <v>91549</v>
+        <v>92286</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,34 +3248,32 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6331023</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis exilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725397</v>
+        <v>725297</v>
       </c>
       <c r="R26" t="n">
-        <v>7179471</v>
+        <v>7179664</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,12 +3308,18 @@
           <t>2025-07-10</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På ordentligt nedbruten granlåga. Hittade ingen ullticka eller violticka trotts en gedigen undersökning. tog kollekt.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590427</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590448</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590429</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590430</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590431</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590432</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590450</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590428</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590452</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590453</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590454</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590455</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590449</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2094,6 +2164,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590445</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2208,6 +2283,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590446</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2322,6 +2402,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590433</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2436,6 +2521,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590435</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2550,6 +2640,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590436</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2664,6 +2759,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590437</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2778,6 +2878,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590438</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2892,6 +2997,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590439</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3006,6 +3116,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590441</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3120,6 +3235,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590442</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3232,6 +3352,11 @@
       <c r="AY25" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590443</t>
         </is>
       </c>
     </row>
@@ -3339,8 +3464,40 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590456</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1316,45 +1316,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126590450</v>
+        <v>136342904</v>
       </c>
       <c r="B8" t="n">
-        <v>91923</v>
+        <v>92080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725319</v>
+        <v>725340</v>
       </c>
       <c r="R8" t="n">
-        <v>7179634</v>
+        <v>7179635</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,12 +1388,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1395,37 +1402,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590450</t>
+          <t>https://artportalen.se/Sighting/136342904</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126590428</v>
+        <v>126590450</v>
       </c>
       <c r="B9" t="n">
-        <v>92281</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725348</v>
+        <v>725319</v>
       </c>
       <c r="R9" t="n">
-        <v>7179632</v>
+        <v>7179634</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,51 +1526,58 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590428</t>
+          <t>https://artportalen.se/Sighting/126590450</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126590452</v>
+        <v>136342841</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>83321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725223</v>
+        <v>725217</v>
       </c>
       <c r="R10" t="n">
-        <v>7179775</v>
+        <v>7179794</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,12 +1604,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,37 +1618,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590452</t>
+          <t>https://artportalen.se/Sighting/136342841</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126590453</v>
+        <v>126590428</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>92281</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725173</v>
+        <v>725348</v>
       </c>
       <c r="R11" t="n">
-        <v>7179703</v>
+        <v>7179632</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,51 +1742,58 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590453</t>
+          <t>https://artportalen.se/Sighting/126590428</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126590454</v>
+        <v>136341406</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>92043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725304</v>
+        <v>725161</v>
       </c>
       <c r="R12" t="n">
-        <v>7179667</v>
+        <v>7179743</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,12 +1820,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1819,72 +1834,76 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590454</t>
+          <t>https://artportalen.se/Sighting/136341406</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126590455</v>
+        <v>136342933</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>92043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725352</v>
+        <v>725334</v>
       </c>
       <c r="R13" t="n">
-        <v>7179640</v>
+        <v>7179647</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,12 +1930,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1925,59 +1944,56 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590455</t>
+          <t>https://artportalen.se/Sighting/136342933</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126590449</v>
+        <v>126590452</v>
       </c>
       <c r="B14" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725329</v>
+        <v>725223</v>
       </c>
       <c r="R14" t="n">
-        <v>7179687</v>
+        <v>7179775</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,59 +2068,51 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590449</t>
+          <t>https://artportalen.se/Sighting/126590452</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126590445</v>
+        <v>126590453</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725301</v>
+        <v>725173</v>
       </c>
       <c r="R15" t="n">
-        <v>7179635</v>
+        <v>7179703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,59 +2174,51 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590445</t>
+          <t>https://artportalen.se/Sighting/126590453</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126590446</v>
+        <v>126590454</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725318</v>
+        <v>725304</v>
       </c>
       <c r="R16" t="n">
-        <v>7179668</v>
+        <v>7179667</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,11 +2253,6 @@
           <t>2025-07-10</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färsk</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2285,59 +2280,51 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590446</t>
+          <t>https://artportalen.se/Sighting/126590454</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126590433</v>
+        <v>126590455</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grötselsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725166</v>
+        <v>725352</v>
       </c>
       <c r="R17" t="n">
-        <v>7179793</v>
+        <v>7179640</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,11 +2359,6 @@
           <t>2025-07-10</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2404,48 +2386,47 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590433</t>
+          <t>https://artportalen.se/Sighting/126590455</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126590435</v>
+        <v>136341087</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>79454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2453,10 +2434,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725121</v>
+        <v>725103</v>
       </c>
       <c r="R18" t="n">
-        <v>7179544</v>
+        <v>7179571</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,17 +2464,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,69 +2478,65 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590435</t>
+          <t>https://artportalen.se/Sighting/136341087</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126590436</v>
+        <v>136342806</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>79454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2572,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725097</v>
+        <v>725183</v>
       </c>
       <c r="R19" t="n">
-        <v>7179606</v>
+        <v>7179872</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,17 +2574,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,69 +2588,65 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590436</t>
+          <t>https://artportalen.se/Sighting/136342806</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126590437</v>
+        <v>136342819</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>79454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2691,10 +2654,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725139</v>
+        <v>725193</v>
       </c>
       <c r="R20" t="n">
-        <v>7179711</v>
+        <v>7179855</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,17 +2684,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2740,69 +2698,65 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590437</t>
+          <t>https://artportalen.se/Sighting/136342819</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126590438</v>
+        <v>136342835</v>
       </c>
       <c r="B21" t="n">
-        <v>57953</v>
+        <v>79454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2810,10 +2764,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>725155</v>
+        <v>725217</v>
       </c>
       <c r="R21" t="n">
-        <v>7179752</v>
+        <v>7179794</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,17 +2794,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2859,69 +2808,65 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590438</t>
+          <t>https://artportalen.se/Sighting/136342835</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126590439</v>
+        <v>136343068</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>79454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2929,10 +2874,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>725273</v>
+        <v>725360</v>
       </c>
       <c r="R22" t="n">
-        <v>7179689</v>
+        <v>7179640</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2959,17 +2904,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2978,69 +2918,65 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590439</t>
+          <t>https://artportalen.se/Sighting/136343068</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126590441</v>
+        <v>136343137</v>
       </c>
       <c r="B23" t="n">
-        <v>57953</v>
+        <v>79454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3048,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>725354</v>
+        <v>725250</v>
       </c>
       <c r="R23" t="n">
-        <v>7179639</v>
+        <v>7179493</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3078,17 +3014,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,69 +3028,65 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590441</t>
+          <t>https://artportalen.se/Sighting/136343137</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126590442</v>
+        <v>136343238</v>
       </c>
       <c r="B24" t="n">
-        <v>57953</v>
+        <v>79454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3167,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>725329</v>
+        <v>725152</v>
       </c>
       <c r="R24" t="n">
-        <v>7179542</v>
+        <v>7179480</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3197,17 +3124,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3216,69 +3138,65 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590442</t>
+          <t>https://artportalen.se/Sighting/136343238</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126590443</v>
+        <v>136343301</v>
       </c>
       <c r="B25" t="n">
-        <v>57953</v>
+        <v>79454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3286,10 +3204,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725244</v>
+        <v>725129</v>
       </c>
       <c r="R25" t="n">
-        <v>7179447</v>
+        <v>7179531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3316,17 +3234,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,58 +3248,64 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126590443</t>
+          <t>https://artportalen.se/Sighting/136343301</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126590456</v>
+        <v>136343335</v>
       </c>
       <c r="B26" t="n">
-        <v>92286</v>
+        <v>79454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6331023</v>
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis exilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Miettinen &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3395,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725297</v>
+        <v>725083</v>
       </c>
       <c r="R26" t="n">
-        <v>7179664</v>
+        <v>7179640</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3425,24 +3344,19 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På ordentligt nedbruten granlåga. Hittade ingen ullticka eller violticka trotts en gedigen undersökning. tog kollekt.</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
@@ -3451,20 +3365,4873 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343335</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126590449</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>725329</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7179687</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr">
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590449</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136343307</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80569</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>725137</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7179526</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>rikligt på en gammal jättesälg</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343307</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136341289</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58001</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>725130</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7179607</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>bohål ca 1m upp i ihålig gran. Hålet är ca 2,5x2,5cm. Mindre hackspett?</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341289</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126590445</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>725301</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7179635</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590445</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126590446</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>725318</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7179668</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färsk</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590446</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136342854</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57985</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>725234</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7179784</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>hål hackat i gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136342854</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126590433</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>725166</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7179793</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590433</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126590435</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>725121</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7179544</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590435</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126590436</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>725097</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7179606</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590436</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126590437</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>725139</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7179711</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590437</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126590438</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>725155</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7179752</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590438</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126590439</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>725273</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7179689</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590439</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126590441</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>725354</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7179639</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590441</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126590442</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>725329</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7179542</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590442</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126590443</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>725244</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7179447</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126590443</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136340912</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>725086</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7179551</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136340912</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136341011</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>725092</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7179560</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341011</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136341119</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>725108</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7179569</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341119</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136341357</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>725214</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7179646</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341357</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136341429</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>725150</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7179759</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341429</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136341497</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>725167</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7179780</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341497</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136341523</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>725169</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7179799</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341523</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136341543</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>725170</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7179829</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341543</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136341560</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>725161</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7179836</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341560</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136341581</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>725164</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7179844</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341581</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136341622</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>725169</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7179849</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341622</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136341629</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>725168</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7179864</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341629</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136341667</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>725168</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7179879</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>ringhack på några olika granar</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136341667</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136342956</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>725331</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7179649</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>typiskt bohål ca 120cm upp i en ihålig gran med tajgagranticka</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136342956</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136342980</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>725343</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7179655</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136342980</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136343099</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>725242</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7179499</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343099</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>136343172</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>725237</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7179459</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>bohål ca 5x5cm ca 3 m upp i en asp. Tretåig?</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343172</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136343199</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>725209</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7179450</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343199</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136343218</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>725194</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7179466</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343218</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>136343251</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>725122</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7179479</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343251</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>136343282</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>725129</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7179488</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343282</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>136343328</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>725111</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7179677</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343328</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136343343</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>725086</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7179612</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343343</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136343375</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>725095</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7179588</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343375</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136343000</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99314</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>725342</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7179659</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>ca 17st överblommade</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343000</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>136343050</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99314</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>725348</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7179649</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>mer än 15st överblommade</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136343050</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126590456</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92286</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6331023</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Skeletocutis exilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Miettinen &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Grötselsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>725297</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7179664</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På ordentligt nedbruten granlåga. Hittade ingen ullticka eller violticka trotts en gedigen undersökning. tog kollekt.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126590456</t>
         </is>
@@ -3497,6 +8264,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136342904</v>
       </c>
       <c r="B8" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136342841</v>
       </c>
       <c r="B10" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136341406</v>
       </c>
       <c r="B12" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136342933</v>
       </c>
       <c r="B13" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136341087</v>
       </c>
       <c r="B18" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>136342806</v>
       </c>
       <c r="B19" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>136342819</v>
       </c>
       <c r="B20" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136342835</v>
       </c>
       <c r="B21" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>136343068</v>
       </c>
       <c r="B22" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>136343137</v>
       </c>
       <c r="B23" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>136343238</v>
       </c>
       <c r="B24" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136343301</v>
       </c>
       <c r="B25" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>136343335</v>
       </c>
       <c r="B26" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136343307</v>
       </c>
       <c r="B28" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136341289</v>
       </c>
       <c r="B29" t="n">
-        <v>58001</v>
+        <v>58006</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>136342854</v>
       </c>
       <c r="B32" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>136340912</v>
       </c>
       <c r="B42" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>136341011</v>
       </c>
       <c r="B43" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>136341119</v>
       </c>
       <c r="B44" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>136341357</v>
       </c>
       <c r="B45" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>136341429</v>
       </c>
       <c r="B46" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136341497</v>
       </c>
       <c r="B47" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>136341523</v>
       </c>
       <c r="B48" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>136341543</v>
       </c>
       <c r="B49" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>136341560</v>
       </c>
       <c r="B50" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>136341581</v>
       </c>
       <c r="B51" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>136341622</v>
       </c>
       <c r="B52" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136341629</v>
       </c>
       <c r="B53" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>136341667</v>
       </c>
       <c r="B54" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>136342956</v>
       </c>
       <c r="B55" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>136342980</v>
       </c>
       <c r="B56" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>136343099</v>
       </c>
       <c r="B57" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136343172</v>
       </c>
       <c r="B58" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>136343199</v>
       </c>
       <c r="B59" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>136343218</v>
       </c>
       <c r="B60" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>136343251</v>
       </c>
       <c r="B61" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>136343282</v>
       </c>
       <c r="B62" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>136343328</v>
       </c>
       <c r="B63" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136343343</v>
       </c>
       <c r="B64" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>136343375</v>
       </c>
       <c r="B65" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>136343000</v>
       </c>
       <c r="B66" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>136343050</v>
       </c>
       <c r="B67" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136342904</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136341406</v>
       </c>
       <c r="B12" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136342933</v>
       </c>
       <c r="B13" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>136343000</v>
       </c>
       <c r="B66" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>136343050</v>
       </c>
       <c r="B67" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136342904</v>
       </c>
       <c r="B8" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136342841</v>
       </c>
       <c r="B10" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136341406</v>
       </c>
       <c r="B12" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136342933</v>
       </c>
       <c r="B13" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136341087</v>
       </c>
       <c r="B18" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>136342806</v>
       </c>
       <c r="B19" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>136342819</v>
       </c>
       <c r="B20" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136342835</v>
       </c>
       <c r="B21" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>136343068</v>
       </c>
       <c r="B22" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>136343137</v>
       </c>
       <c r="B23" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>136343238</v>
       </c>
       <c r="B24" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136343301</v>
       </c>
       <c r="B25" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>136343335</v>
       </c>
       <c r="B26" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136343307</v>
       </c>
       <c r="B28" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>136341289</v>
       </c>
       <c r="B29" t="n">
-        <v>58006</v>
+        <v>58019</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>136342854</v>
       </c>
       <c r="B32" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>136340912</v>
       </c>
       <c r="B42" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>136341011</v>
       </c>
       <c r="B43" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>136341119</v>
       </c>
       <c r="B44" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>136341357</v>
       </c>
       <c r="B45" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>136341429</v>
       </c>
       <c r="B46" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136341497</v>
       </c>
       <c r="B47" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>136341523</v>
       </c>
       <c r="B48" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>136341543</v>
       </c>
       <c r="B49" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>136341560</v>
       </c>
       <c r="B50" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>136341581</v>
       </c>
       <c r="B51" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>136341622</v>
       </c>
       <c r="B52" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>136341629</v>
       </c>
       <c r="B53" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>136341667</v>
       </c>
       <c r="B54" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>136342956</v>
       </c>
       <c r="B55" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>136342980</v>
       </c>
       <c r="B56" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>136343099</v>
       </c>
       <c r="B57" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>136343172</v>
       </c>
       <c r="B58" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>136343199</v>
       </c>
       <c r="B59" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>136343218</v>
       </c>
       <c r="B60" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>136343251</v>
       </c>
       <c r="B61" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>136343282</v>
       </c>
       <c r="B62" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>136343328</v>
       </c>
       <c r="B63" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136343343</v>
       </c>
       <c r="B64" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>136343375</v>
       </c>
       <c r="B65" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>136343000</v>
       </c>
       <c r="B66" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>136343050</v>
       </c>
       <c r="B67" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 28986-2025 artfynd.xlsx
+++ b/artfynd/A 28986-2025 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136342904</v>
       </c>
       <c r="B8" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136342841</v>
       </c>
       <c r="B10" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>136341406</v>
       </c>
       <c r="B12" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136342933</v>
       </c>
       <c r="B13" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>136341087</v>
       </c>
       <c r="B18" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>136342806</v>
       </c>
       <c r="B19" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>136342819</v>
       </c>
       <c r="B20" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>136342835</v>
       </c>
       <c r="B21" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>136343068</v>
       </c>
       <c r="B22" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>136343137</v>
       </c>
       <c r="B23" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>136343238</v>
       </c>
       <c r="B24" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>136343301</v>
       </c>
       <c r="B25" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>136343335</v>
       </c>
       <c r="B26" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136343307</v>
       </c>
       <c r="B28" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>136343000</v>
       </c>
       <c r="B66" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>136343050</v>
       </c>
       <c r="B67" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
